--- a/Media/Template/Template-rpt_Member_Card.xlsx
+++ b/Media/Template/Template-rpt_Member_Card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DuyTu_E\SourceCode\ReportCenter\Report_Center\Media\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9063A138-3663-435A-AADC-911104020119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCB3CE0-EF82-414E-8B56-9C0EE4AD121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7DC8410E-D653-43DB-960E-BCBF44B6A00B}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -174,19 +173,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -197,6 +189,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -543,93 +546,93 @@
     <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
